--- a/kits/weekly-digest/samples/battery-storage-ohio-week41/output/battery-storage-zoning-watch-ohio-2026-10-08.xlsx
+++ b/kits/weekly-digest/samples/battery-storage-ohio-week41/output/battery-storage-zoning-watch-ohio-2026-10-08.xlsx
@@ -528,7 +528,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -695,6 +695,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
